--- a/excel/260817哥布林弹珠攻略.xlsx
+++ b/excel/260817哥布林弹珠攻略.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\卡皮模拟\攻略图生成器\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB93FD3D-CD0E-4772-8708-02CB45F631EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76459C3D-38FE-4EEE-BB91-E1A165408D4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -555,27 +555,6 @@
     <phoneticPr fontId="24" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">可兑换： </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>觉醒核心自选箱×1 + SS限定烙印自选箱×1 + S装备自选箱×1</t>
-    </r>
-    <phoneticPr fontId="24" type="noConversion"/>
-  </si>
-  <si>
-    <t>哥布林弹珠｜1.3钻攻略</t>
-    <phoneticPr fontId="24" type="noConversion"/>
-  </si>
-  <si>
     <t>① 任务125券
 ② 攒券不用</t>
     <phoneticPr fontId="24" type="noConversion"/>
@@ -658,6 +637,27 @@
       </rPr>
       <t xml:space="preserve">觉醒核心自选箱×2 + SS限定烙印自选箱×1 </t>
     </r>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">可兑换： </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>觉醒核心自选箱×1 + SS限定烙印自选箱×1 + S装备自选箱×1 或 S武器自选箱×1</t>
+    </r>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <t>哥布林弹珠｜1.3万钻攻略</t>
     <phoneticPr fontId="24" type="noConversion"/>
   </si>
 </sst>
@@ -1994,15 +1994,24 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2032,15 +2041,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="22" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="8">
@@ -2435,7 +2435,7 @@
         <v>69</v>
       </c>
       <c r="C3" s="119" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D3" s="119">
         <v>1</v>
@@ -3588,34 +3588,34 @@
     <row r="1" spans="2:16" ht="16.2" thickBot="1"/>
     <row r="2" spans="2:16" ht="16.2" thickTop="1">
       <c r="B2" s="14"/>
-      <c r="C2" s="167" t="s">
+      <c r="C2" s="168" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="168"/>
-      <c r="E2" s="167" t="s">
+      <c r="D2" s="169"/>
+      <c r="E2" s="168" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="168"/>
-      <c r="G2" s="167" t="s">
+      <c r="F2" s="169"/>
+      <c r="G2" s="168" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="168"/>
-      <c r="I2" s="167" t="s">
+      <c r="H2" s="169"/>
+      <c r="I2" s="168" t="s">
         <v>28</v>
       </c>
-      <c r="J2" s="168"/>
-      <c r="K2" s="167" t="s">
+      <c r="J2" s="169"/>
+      <c r="K2" s="168" t="s">
         <v>29</v>
       </c>
-      <c r="L2" s="168"/>
-      <c r="M2" s="167" t="s">
+      <c r="L2" s="169"/>
+      <c r="M2" s="168" t="s">
         <v>30</v>
       </c>
-      <c r="N2" s="168"/>
-      <c r="O2" s="167" t="s">
+      <c r="N2" s="169"/>
+      <c r="O2" s="168" t="s">
         <v>31</v>
       </c>
-      <c r="P2" s="168"/>
+      <c r="P2" s="169"/>
     </row>
     <row r="3" spans="2:16" ht="16.2" thickBot="1">
       <c r="B3" s="15"/>
@@ -4726,7 +4726,7 @@
       <c r="P25" s="13"/>
     </row>
     <row r="26" spans="2:16" ht="16.2" thickTop="1">
-      <c r="B26" s="169" t="s">
+      <c r="B26" s="172" t="s">
         <v>48</v>
       </c>
       <c r="C26" s="20">
@@ -4773,7 +4773,7 @@
       </c>
     </row>
     <row r="27" spans="2:16">
-      <c r="B27" s="170"/>
+      <c r="B27" s="173"/>
       <c r="C27" s="76">
         <v>0</v>
       </c>
@@ -4818,7 +4818,7 @@
       </c>
     </row>
     <row r="28" spans="2:16" ht="16.2" thickBot="1">
-      <c r="B28" s="171"/>
+      <c r="B28" s="174"/>
       <c r="C28" s="77"/>
       <c r="D28" s="78"/>
       <c r="E28" s="77"/>
@@ -4835,7 +4835,7 @@
       <c r="P28" s="78"/>
     </row>
     <row r="29" spans="2:16" ht="16.2" thickTop="1">
-      <c r="B29" s="170" t="s">
+      <c r="B29" s="173" t="s">
         <v>49</v>
       </c>
       <c r="C29" s="20">
@@ -4896,7 +4896,7 @@
       </c>
     </row>
     <row r="30" spans="2:16">
-      <c r="B30" s="170"/>
+      <c r="B30" s="173"/>
       <c r="C30" s="76">
         <f>IFERROR(LOOKUP(C27,价格6:价格648,翡翠100:翡翠10000),0)</f>
         <v>0</v>
@@ -4954,7 +4954,7 @@
       </c>
     </row>
     <row r="31" spans="2:16" ht="16.2" thickBot="1">
-      <c r="B31" s="171"/>
+      <c r="B31" s="174"/>
       <c r="C31" s="77"/>
       <c r="D31" s="78"/>
       <c r="E31" s="77"/>
@@ -4971,52 +4971,52 @@
       <c r="P31" s="78"/>
     </row>
     <row r="32" spans="2:16" ht="24.6" customHeight="1" thickTop="1">
-      <c r="B32" s="170" t="s">
+      <c r="B32" s="173" t="s">
         <v>46</v>
       </c>
-      <c r="C32" s="172" t="str">
+      <c r="C32" s="175" t="str">
         <f>SUM(C6,E6,G6,I6,K6,M6,O6)*钻石购买 &amp;"钻石"</f>
         <v>50400钻石</v>
       </c>
-      <c r="D32" s="173"/>
-      <c r="E32" s="173"/>
-      <c r="F32" s="173"/>
-      <c r="G32" s="173"/>
-      <c r="H32" s="173"/>
-      <c r="I32" s="178" t="str">
+      <c r="D32" s="176"/>
+      <c r="E32" s="176"/>
+      <c r="F32" s="176"/>
+      <c r="G32" s="176"/>
+      <c r="H32" s="176"/>
+      <c r="I32" s="181" t="str">
         <f>SUM(C26:P28) &amp;"元"</f>
         <v>0元</v>
       </c>
-      <c r="J32" s="178"/>
-      <c r="K32" s="178"/>
-      <c r="L32" s="178"/>
-      <c r="M32" s="179" t="str">
+      <c r="J32" s="181"/>
+      <c r="K32" s="181"/>
+      <c r="L32" s="181"/>
+      <c r="M32" s="166" t="str">
         <f>SUM(C29:P31) &amp; "翡翠"</f>
         <v>0翡翠</v>
       </c>
-      <c r="N32" s="179"/>
-      <c r="O32" s="179"/>
-      <c r="P32" s="180"/>
+      <c r="N32" s="166"/>
+      <c r="O32" s="166"/>
+      <c r="P32" s="167"/>
     </row>
     <row r="33" spans="2:19" ht="22.8" thickBot="1">
-      <c r="B33" s="171"/>
-      <c r="C33" s="175" t="str">
+      <c r="B33" s="174"/>
+      <c r="C33" s="178" t="str">
         <f>"最终收益："&amp;ROUNDDOWN(O25,0)&amp;B25&amp;"+"&amp;ROUNDDOWN(O24,0)&amp;B24</f>
         <v>最终收益：901高级卷轴+21198普通卷轴</v>
       </c>
-      <c r="D33" s="176"/>
-      <c r="E33" s="176"/>
-      <c r="F33" s="176"/>
-      <c r="G33" s="176"/>
-      <c r="H33" s="176"/>
-      <c r="I33" s="176"/>
-      <c r="J33" s="176"/>
-      <c r="K33" s="176"/>
-      <c r="L33" s="176"/>
-      <c r="M33" s="176"/>
-      <c r="N33" s="176"/>
-      <c r="O33" s="176"/>
-      <c r="P33" s="177"/>
+      <c r="D33" s="179"/>
+      <c r="E33" s="179"/>
+      <c r="F33" s="179"/>
+      <c r="G33" s="179"/>
+      <c r="H33" s="179"/>
+      <c r="I33" s="179"/>
+      <c r="J33" s="179"/>
+      <c r="K33" s="179"/>
+      <c r="L33" s="179"/>
+      <c r="M33" s="179"/>
+      <c r="N33" s="179"/>
+      <c r="O33" s="179"/>
+      <c r="P33" s="180"/>
     </row>
     <row r="34" spans="2:19" ht="16.2" thickTop="1"/>
     <row r="38" spans="2:19" ht="38.4" customHeight="1"/>
@@ -5089,18 +5089,18 @@
       <c r="P42" s="10"/>
     </row>
     <row r="43" spans="2:19">
-      <c r="F43" s="174"/>
-      <c r="G43" s="174"/>
-      <c r="H43" s="174"/>
-      <c r="I43" s="174"/>
-      <c r="K43" s="181"/>
-      <c r="L43" s="181"/>
-      <c r="M43" s="181"/>
-      <c r="N43" s="181"/>
-      <c r="P43" s="181"/>
-      <c r="Q43" s="181"/>
-      <c r="R43" s="181"/>
-      <c r="S43" s="181"/>
+      <c r="F43" s="177"/>
+      <c r="G43" s="177"/>
+      <c r="H43" s="177"/>
+      <c r="I43" s="177"/>
+      <c r="K43" s="170"/>
+      <c r="L43" s="170"/>
+      <c r="M43" s="170"/>
+      <c r="N43" s="170"/>
+      <c r="P43" s="170"/>
+      <c r="Q43" s="170"/>
+      <c r="R43" s="170"/>
+      <c r="S43" s="170"/>
     </row>
     <row r="44" spans="2:19">
       <c r="K44" s="6"/>
@@ -5159,13 +5159,13 @@
       <c r="P49" s="6"/>
     </row>
     <row r="50" spans="2:16">
-      <c r="B50" s="166"/>
-      <c r="C50" s="166"/>
-      <c r="D50" s="166"/>
-      <c r="K50" s="181"/>
-      <c r="L50" s="181"/>
-      <c r="M50" s="181"/>
-      <c r="N50" s="181"/>
+      <c r="B50" s="171"/>
+      <c r="C50" s="171"/>
+      <c r="D50" s="171"/>
+      <c r="K50" s="170"/>
+      <c r="L50" s="170"/>
+      <c r="M50" s="170"/>
+      <c r="N50" s="170"/>
     </row>
     <row r="51" spans="2:16">
       <c r="K51" s="6"/>
@@ -5186,9 +5186,9 @@
       <c r="P53" s="25"/>
     </row>
     <row r="54" spans="2:16">
-      <c r="B54" s="166"/>
-      <c r="C54" s="166"/>
-      <c r="D54" s="166"/>
+      <c r="B54" s="171"/>
+      <c r="C54" s="171"/>
+      <c r="D54" s="171"/>
       <c r="K54" s="6"/>
       <c r="M54" s="6"/>
       <c r="N54" s="6"/>
@@ -5268,7 +5268,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="M2:N2"/>
     <mergeCell ref="P43:S43"/>
     <mergeCell ref="K43:N43"/>
     <mergeCell ref="K50:N50"/>
@@ -5288,6 +5287,7 @@
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
   </mergeCells>
   <phoneticPr fontId="24" type="noConversion"/>
   <conditionalFormatting sqref="B6:P6">
@@ -5912,34 +5912,34 @@
     <row r="1" spans="2:16" ht="16.2" thickBot="1"/>
     <row r="2" spans="2:16" ht="16.2" thickTop="1">
       <c r="B2" s="14"/>
-      <c r="C2" s="167" t="s">
+      <c r="C2" s="168" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="168"/>
-      <c r="E2" s="167" t="s">
+      <c r="D2" s="169"/>
+      <c r="E2" s="168" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="168"/>
-      <c r="G2" s="167" t="s">
+      <c r="F2" s="169"/>
+      <c r="G2" s="168" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="168"/>
-      <c r="I2" s="167" t="s">
+      <c r="H2" s="169"/>
+      <c r="I2" s="168" t="s">
         <v>28</v>
       </c>
-      <c r="J2" s="168"/>
-      <c r="K2" s="167" t="s">
+      <c r="J2" s="169"/>
+      <c r="K2" s="168" t="s">
         <v>29</v>
       </c>
-      <c r="L2" s="168"/>
-      <c r="M2" s="167" t="s">
+      <c r="L2" s="169"/>
+      <c r="M2" s="168" t="s">
         <v>30</v>
       </c>
-      <c r="N2" s="168"/>
-      <c r="O2" s="167" t="s">
+      <c r="N2" s="169"/>
+      <c r="O2" s="168" t="s">
         <v>31</v>
       </c>
-      <c r="P2" s="168"/>
+      <c r="P2" s="169"/>
     </row>
     <row r="3" spans="2:16" ht="16.2" thickBot="1">
       <c r="B3" s="15"/>
@@ -7050,7 +7050,7 @@
       <c r="P25" s="13"/>
     </row>
     <row r="26" spans="2:16" ht="16.2" thickTop="1">
-      <c r="B26" s="169" t="s">
+      <c r="B26" s="172" t="s">
         <v>48</v>
       </c>
       <c r="C26" s="20">
@@ -7097,7 +7097,7 @@
       </c>
     </row>
     <row r="27" spans="2:16">
-      <c r="B27" s="170"/>
+      <c r="B27" s="173"/>
       <c r="C27" s="76">
         <v>0</v>
       </c>
@@ -7142,7 +7142,7 @@
       </c>
     </row>
     <row r="28" spans="2:16" ht="16.2" thickBot="1">
-      <c r="B28" s="171"/>
+      <c r="B28" s="174"/>
       <c r="C28" s="77"/>
       <c r="D28" s="78"/>
       <c r="E28" s="77"/>
@@ -7159,7 +7159,7 @@
       <c r="P28" s="78"/>
     </row>
     <row r="29" spans="2:16" ht="16.2" thickTop="1">
-      <c r="B29" s="170" t="s">
+      <c r="B29" s="173" t="s">
         <v>49</v>
       </c>
       <c r="C29" s="20">
@@ -7220,7 +7220,7 @@
       </c>
     </row>
     <row r="30" spans="2:16">
-      <c r="B30" s="170"/>
+      <c r="B30" s="173"/>
       <c r="C30" s="76">
         <f>IFERROR(LOOKUP(C27,价格6:价格648,翡翠100:翡翠10000),0)</f>
         <v>0</v>
@@ -7278,7 +7278,7 @@
       </c>
     </row>
     <row r="31" spans="2:16" ht="16.2" thickBot="1">
-      <c r="B31" s="171"/>
+      <c r="B31" s="174"/>
       <c r="C31" s="77"/>
       <c r="D31" s="78"/>
       <c r="E31" s="77"/>
@@ -7295,52 +7295,52 @@
       <c r="P31" s="78"/>
     </row>
     <row r="32" spans="2:16" ht="24.6" customHeight="1" thickTop="1">
-      <c r="B32" s="170" t="s">
+      <c r="B32" s="173" t="s">
         <v>46</v>
       </c>
-      <c r="C32" s="172" t="str">
+      <c r="C32" s="175" t="str">
         <f>SUM(C6,E6,G6,I6,K6,M6,O6)*钻石购买 &amp;"钻石"</f>
         <v>12900钻石</v>
       </c>
-      <c r="D32" s="173"/>
-      <c r="E32" s="173"/>
-      <c r="F32" s="173"/>
-      <c r="G32" s="173"/>
-      <c r="H32" s="173"/>
-      <c r="I32" s="178" t="str">
+      <c r="D32" s="176"/>
+      <c r="E32" s="176"/>
+      <c r="F32" s="176"/>
+      <c r="G32" s="176"/>
+      <c r="H32" s="176"/>
+      <c r="I32" s="181" t="str">
         <f>SUM(C26:P28) &amp;"元"</f>
         <v>0元</v>
       </c>
-      <c r="J32" s="178"/>
-      <c r="K32" s="178"/>
-      <c r="L32" s="178"/>
-      <c r="M32" s="179" t="str">
+      <c r="J32" s="181"/>
+      <c r="K32" s="181"/>
+      <c r="L32" s="181"/>
+      <c r="M32" s="166" t="str">
         <f>SUM(C29:P31) &amp; "翡翠"</f>
         <v>0翡翠</v>
       </c>
-      <c r="N32" s="179"/>
-      <c r="O32" s="179"/>
-      <c r="P32" s="180"/>
+      <c r="N32" s="166"/>
+      <c r="O32" s="166"/>
+      <c r="P32" s="167"/>
     </row>
     <row r="33" spans="2:19" ht="22.8" thickBot="1">
-      <c r="B33" s="171"/>
-      <c r="C33" s="175" t="str">
+      <c r="B33" s="174"/>
+      <c r="C33" s="178" t="str">
         <f>"最终收益："&amp;ROUNDDOWN(O25,0)&amp;B25&amp;"+"&amp;ROUNDDOWN(O24,0)&amp;B24</f>
         <v>最终收益：540高级卷轴+14335普通卷轴</v>
       </c>
-      <c r="D33" s="176"/>
-      <c r="E33" s="176"/>
-      <c r="F33" s="176"/>
-      <c r="G33" s="176"/>
-      <c r="H33" s="176"/>
-      <c r="I33" s="176"/>
-      <c r="J33" s="176"/>
-      <c r="K33" s="176"/>
-      <c r="L33" s="176"/>
-      <c r="M33" s="176"/>
-      <c r="N33" s="176"/>
-      <c r="O33" s="176"/>
-      <c r="P33" s="177"/>
+      <c r="D33" s="179"/>
+      <c r="E33" s="179"/>
+      <c r="F33" s="179"/>
+      <c r="G33" s="179"/>
+      <c r="H33" s="179"/>
+      <c r="I33" s="179"/>
+      <c r="J33" s="179"/>
+      <c r="K33" s="179"/>
+      <c r="L33" s="179"/>
+      <c r="M33" s="179"/>
+      <c r="N33" s="179"/>
+      <c r="O33" s="179"/>
+      <c r="P33" s="180"/>
     </row>
     <row r="34" spans="2:19" ht="16.2" thickTop="1"/>
     <row r="38" spans="2:19" ht="38.4" customHeight="1"/>
@@ -7413,18 +7413,18 @@
       <c r="P42" s="10"/>
     </row>
     <row r="43" spans="2:19">
-      <c r="F43" s="174"/>
-      <c r="G43" s="174"/>
-      <c r="H43" s="174"/>
-      <c r="I43" s="174"/>
-      <c r="K43" s="181"/>
-      <c r="L43" s="181"/>
-      <c r="M43" s="181"/>
-      <c r="N43" s="181"/>
-      <c r="P43" s="181"/>
-      <c r="Q43" s="181"/>
-      <c r="R43" s="181"/>
-      <c r="S43" s="181"/>
+      <c r="F43" s="177"/>
+      <c r="G43" s="177"/>
+      <c r="H43" s="177"/>
+      <c r="I43" s="177"/>
+      <c r="K43" s="170"/>
+      <c r="L43" s="170"/>
+      <c r="M43" s="170"/>
+      <c r="N43" s="170"/>
+      <c r="P43" s="170"/>
+      <c r="Q43" s="170"/>
+      <c r="R43" s="170"/>
+      <c r="S43" s="170"/>
     </row>
     <row r="44" spans="2:19">
       <c r="K44" s="6"/>
@@ -7483,13 +7483,13 @@
       <c r="P49" s="6"/>
     </row>
     <row r="50" spans="2:16">
-      <c r="B50" s="166"/>
-      <c r="C50" s="166"/>
-      <c r="D50" s="166"/>
-      <c r="K50" s="181"/>
-      <c r="L50" s="181"/>
-      <c r="M50" s="181"/>
-      <c r="N50" s="181"/>
+      <c r="B50" s="171"/>
+      <c r="C50" s="171"/>
+      <c r="D50" s="171"/>
+      <c r="K50" s="170"/>
+      <c r="L50" s="170"/>
+      <c r="M50" s="170"/>
+      <c r="N50" s="170"/>
     </row>
     <row r="51" spans="2:16">
       <c r="K51" s="6"/>
@@ -7510,9 +7510,9 @@
       <c r="P53" s="25"/>
     </row>
     <row r="54" spans="2:16">
-      <c r="B54" s="166"/>
-      <c r="C54" s="166"/>
-      <c r="D54" s="166"/>
+      <c r="B54" s="171"/>
+      <c r="C54" s="171"/>
+      <c r="D54" s="171"/>
       <c r="K54" s="6"/>
       <c r="M54" s="6"/>
       <c r="N54" s="6"/>
@@ -7592,7 +7592,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B54:D54"/>
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="B26:B28"/>
     <mergeCell ref="B29:B31"/>
@@ -7607,11 +7606,12 @@
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="M2:N2"/>
-    <mergeCell ref="F43:I43"/>
     <mergeCell ref="K43:N43"/>
     <mergeCell ref="P43:S43"/>
     <mergeCell ref="B50:D50"/>
     <mergeCell ref="K50:N50"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="F43:I43"/>
   </mergeCells>
   <phoneticPr fontId="24" type="noConversion"/>
   <conditionalFormatting sqref="B6:P6">
@@ -7677,7 +7677,7 @@
     <row r="1" spans="2:21" ht="16.2" thickBot="1"/>
     <row r="2" spans="2:21" ht="24" customHeight="1" thickTop="1" thickBot="1">
       <c r="B2" s="133" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="C2" s="134"/>
       <c r="D2" s="134"/>
@@ -7768,7 +7768,7 @@
     </row>
     <row r="8" spans="2:21" ht="17.55" customHeight="1" thickTop="1">
       <c r="B8" s="121" t="s">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="C8" s="122"/>
       <c r="D8" s="122"/>
@@ -7872,7 +7872,7 @@
         <v>37</v>
       </c>
       <c r="C13" s="35" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D13" s="35" t="str">
         <f>哥布林弹珠1.3w!E20</f>
@@ -7905,7 +7905,7 @@
         <v>38</v>
       </c>
       <c r="C14" s="35" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>哥布林弹珠1.3w!G20</f>
@@ -7938,7 +7938,7 @@
         <v>39</v>
       </c>
       <c r="C15" s="35" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D15" s="35" t="str">
         <f>哥布林弹珠1.3w!I20</f>
@@ -7971,7 +7971,7 @@
         <v>40</v>
       </c>
       <c r="C16" s="35" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D16" s="35" t="str">
         <f>哥布林弹珠1.3w!K20</f>
@@ -8004,7 +8004,7 @@
         <v>41</v>
       </c>
       <c r="C17" s="35" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D17" s="35" t="str">
         <f>哥布林弹珠1.3w!M20</f>
@@ -8040,7 +8040,7 @@
         <v>42</v>
       </c>
       <c r="C18" s="47" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D18" s="48" t="str">
         <f>哥布林弹珠1.3w!O20</f>
@@ -8094,7 +8094,7 @@
     </row>
     <row r="21" spans="1:18" ht="66" customHeight="1" thickBot="1">
       <c r="B21" s="130" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C21" s="131"/>
       <c r="D21" s="131"/>
@@ -8237,34 +8237,34 @@
     <row r="1" spans="2:18" ht="16.2" thickBot="1"/>
     <row r="2" spans="2:18" ht="16.2" thickTop="1">
       <c r="B2" s="14"/>
-      <c r="C2" s="167" t="s">
+      <c r="C2" s="168" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="168"/>
-      <c r="E2" s="167" t="s">
+      <c r="D2" s="169"/>
+      <c r="E2" s="168" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="168"/>
-      <c r="G2" s="167" t="s">
+      <c r="F2" s="169"/>
+      <c r="G2" s="168" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="168"/>
-      <c r="I2" s="167" t="s">
+      <c r="H2" s="169"/>
+      <c r="I2" s="168" t="s">
         <v>28</v>
       </c>
-      <c r="J2" s="168"/>
-      <c r="K2" s="167" t="s">
+      <c r="J2" s="169"/>
+      <c r="K2" s="168" t="s">
         <v>29</v>
       </c>
-      <c r="L2" s="168"/>
-      <c r="M2" s="167" t="s">
+      <c r="L2" s="169"/>
+      <c r="M2" s="168" t="s">
         <v>30</v>
       </c>
-      <c r="N2" s="168"/>
-      <c r="O2" s="167" t="s">
+      <c r="N2" s="169"/>
+      <c r="O2" s="168" t="s">
         <v>31</v>
       </c>
-      <c r="P2" s="168"/>
+      <c r="P2" s="169"/>
     </row>
     <row r="3" spans="2:18" ht="16.2" thickBot="1">
       <c r="B3" s="15"/>
@@ -8903,7 +8903,7 @@
         <v>1128.05</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="16" spans="2:18" ht="16.2" thickBot="1">
@@ -9389,7 +9389,7 @@
       <c r="P25" s="13"/>
     </row>
     <row r="26" spans="2:16" ht="16.2" thickTop="1">
-      <c r="B26" s="169" t="s">
+      <c r="B26" s="172" t="s">
         <v>48</v>
       </c>
       <c r="C26" s="20">
@@ -9436,7 +9436,7 @@
       </c>
     </row>
     <row r="27" spans="2:16">
-      <c r="B27" s="170"/>
+      <c r="B27" s="173"/>
       <c r="C27" s="76">
         <v>0</v>
       </c>
@@ -9481,7 +9481,7 @@
       </c>
     </row>
     <row r="28" spans="2:16" ht="16.2" thickBot="1">
-      <c r="B28" s="171"/>
+      <c r="B28" s="174"/>
       <c r="C28" s="77"/>
       <c r="D28" s="78"/>
       <c r="E28" s="77"/>
@@ -9498,7 +9498,7 @@
       <c r="P28" s="78"/>
     </row>
     <row r="29" spans="2:16" ht="16.2" thickTop="1">
-      <c r="B29" s="170" t="s">
+      <c r="B29" s="173" t="s">
         <v>49</v>
       </c>
       <c r="C29" s="20">
@@ -9559,7 +9559,7 @@
       </c>
     </row>
     <row r="30" spans="2:16">
-      <c r="B30" s="170"/>
+      <c r="B30" s="173"/>
       <c r="C30" s="76">
         <f>IFERROR(LOOKUP(C27,价格6:价格648,翡翠100:翡翠10000),0)</f>
         <v>0</v>
@@ -9617,7 +9617,7 @@
       </c>
     </row>
     <row r="31" spans="2:16" ht="16.2" thickBot="1">
-      <c r="B31" s="171"/>
+      <c r="B31" s="174"/>
       <c r="C31" s="77"/>
       <c r="D31" s="78"/>
       <c r="E31" s="77"/>
@@ -9634,52 +9634,52 @@
       <c r="P31" s="78"/>
     </row>
     <row r="32" spans="2:16" ht="24.6" customHeight="1" thickTop="1">
-      <c r="B32" s="170" t="s">
+      <c r="B32" s="173" t="s">
         <v>46</v>
       </c>
-      <c r="C32" s="172" t="str">
+      <c r="C32" s="175" t="str">
         <f>SUM(C6,E6,G6,I6,K6,M6,O6)*钻石购买 &amp;"钻石"</f>
         <v>50400钻石</v>
       </c>
-      <c r="D32" s="173"/>
-      <c r="E32" s="173"/>
-      <c r="F32" s="173"/>
-      <c r="G32" s="173"/>
-      <c r="H32" s="173"/>
-      <c r="I32" s="178" t="str">
+      <c r="D32" s="176"/>
+      <c r="E32" s="176"/>
+      <c r="F32" s="176"/>
+      <c r="G32" s="176"/>
+      <c r="H32" s="176"/>
+      <c r="I32" s="181" t="str">
         <f>SUM(C26:P28) &amp;"元"</f>
         <v>294元</v>
       </c>
-      <c r="J32" s="178"/>
-      <c r="K32" s="178"/>
-      <c r="L32" s="178"/>
-      <c r="M32" s="179" t="str">
+      <c r="J32" s="181"/>
+      <c r="K32" s="181"/>
+      <c r="L32" s="181"/>
+      <c r="M32" s="166" t="str">
         <f>SUM(C29:P31) &amp; "翡翠"</f>
         <v>4500翡翠</v>
       </c>
-      <c r="N32" s="179"/>
-      <c r="O32" s="179"/>
-      <c r="P32" s="180"/>
+      <c r="N32" s="166"/>
+      <c r="O32" s="166"/>
+      <c r="P32" s="167"/>
     </row>
     <row r="33" spans="2:19" ht="22.8" thickBot="1">
-      <c r="B33" s="171"/>
-      <c r="C33" s="175" t="str">
+      <c r="B33" s="174"/>
+      <c r="C33" s="178" t="str">
         <f>"最终收益："&amp;ROUNDDOWN(O25,0)&amp;B25&amp;"+"&amp;ROUNDDOWN(O24,0)&amp;B24</f>
         <v>最终收益：1871高级卷轴+22803普通卷轴</v>
       </c>
-      <c r="D33" s="176"/>
-      <c r="E33" s="176"/>
-      <c r="F33" s="176"/>
-      <c r="G33" s="176"/>
-      <c r="H33" s="176"/>
-      <c r="I33" s="176"/>
-      <c r="J33" s="176"/>
-      <c r="K33" s="176"/>
-      <c r="L33" s="176"/>
-      <c r="M33" s="176"/>
-      <c r="N33" s="176"/>
-      <c r="O33" s="176"/>
-      <c r="P33" s="177"/>
+      <c r="D33" s="179"/>
+      <c r="E33" s="179"/>
+      <c r="F33" s="179"/>
+      <c r="G33" s="179"/>
+      <c r="H33" s="179"/>
+      <c r="I33" s="179"/>
+      <c r="J33" s="179"/>
+      <c r="K33" s="179"/>
+      <c r="L33" s="179"/>
+      <c r="M33" s="179"/>
+      <c r="N33" s="179"/>
+      <c r="O33" s="179"/>
+      <c r="P33" s="180"/>
     </row>
     <row r="34" spans="2:19" ht="16.2" thickTop="1"/>
     <row r="38" spans="2:19" ht="38.4" customHeight="1"/>
@@ -9752,18 +9752,18 @@
       <c r="P42" s="10"/>
     </row>
     <row r="43" spans="2:19">
-      <c r="F43" s="174"/>
-      <c r="G43" s="174"/>
-      <c r="H43" s="174"/>
-      <c r="I43" s="174"/>
-      <c r="K43" s="181"/>
-      <c r="L43" s="181"/>
-      <c r="M43" s="181"/>
-      <c r="N43" s="181"/>
-      <c r="P43" s="181"/>
-      <c r="Q43" s="181"/>
-      <c r="R43" s="181"/>
-      <c r="S43" s="181"/>
+      <c r="F43" s="177"/>
+      <c r="G43" s="177"/>
+      <c r="H43" s="177"/>
+      <c r="I43" s="177"/>
+      <c r="K43" s="170"/>
+      <c r="L43" s="170"/>
+      <c r="M43" s="170"/>
+      <c r="N43" s="170"/>
+      <c r="P43" s="170"/>
+      <c r="Q43" s="170"/>
+      <c r="R43" s="170"/>
+      <c r="S43" s="170"/>
     </row>
     <row r="44" spans="2:19">
       <c r="K44" s="6"/>
@@ -9822,13 +9822,13 @@
       <c r="P49" s="6"/>
     </row>
     <row r="50" spans="2:16">
-      <c r="B50" s="166"/>
-      <c r="C50" s="166"/>
-      <c r="D50" s="166"/>
-      <c r="K50" s="181"/>
-      <c r="L50" s="181"/>
-      <c r="M50" s="181"/>
-      <c r="N50" s="181"/>
+      <c r="B50" s="171"/>
+      <c r="C50" s="171"/>
+      <c r="D50" s="171"/>
+      <c r="K50" s="170"/>
+      <c r="L50" s="170"/>
+      <c r="M50" s="170"/>
+      <c r="N50" s="170"/>
     </row>
     <row r="51" spans="2:16">
       <c r="K51" s="6"/>
@@ -9849,9 +9849,9 @@
       <c r="P53" s="25"/>
     </row>
     <row r="54" spans="2:16">
-      <c r="B54" s="166"/>
-      <c r="C54" s="166"/>
-      <c r="D54" s="166"/>
+      <c r="B54" s="171"/>
+      <c r="C54" s="171"/>
+      <c r="D54" s="171"/>
       <c r="K54" s="6"/>
       <c r="M54" s="6"/>
       <c r="N54" s="6"/>
@@ -9931,7 +9931,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B54:D54"/>
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="B26:B28"/>
     <mergeCell ref="B29:B31"/>
@@ -9946,11 +9945,12 @@
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="M2:N2"/>
-    <mergeCell ref="F43:I43"/>
     <mergeCell ref="K43:N43"/>
     <mergeCell ref="P43:S43"/>
     <mergeCell ref="B50:D50"/>
     <mergeCell ref="K50:N50"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="F43:I43"/>
   </mergeCells>
   <phoneticPr fontId="24" type="noConversion"/>
   <conditionalFormatting sqref="B6:P6">
@@ -10016,7 +10016,7 @@
     <row r="1" spans="1:21" ht="16.2" thickBot="1"/>
     <row r="2" spans="1:21" ht="24" customHeight="1" thickTop="1" thickBot="1">
       <c r="B2" s="133" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C2" s="134"/>
       <c r="D2" s="134"/>
@@ -10107,7 +10107,7 @@
     </row>
     <row r="8" spans="1:21" ht="17.55" customHeight="1" thickTop="1">
       <c r="B8" s="121" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C8" s="122"/>
       <c r="D8" s="122"/>
@@ -10175,13 +10175,13 @@
     </row>
     <row r="12" spans="1:21" ht="36">
       <c r="A12" s="34" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B12" s="41" t="s">
         <v>36</v>
       </c>
       <c r="C12" s="37" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D12" s="37" t="str">
         <f>哥布林弹珠氪金!C20</f>
@@ -10211,13 +10211,13 @@
     </row>
     <row r="13" spans="1:21" ht="39.6">
       <c r="A13" s="34" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B13" s="39" t="s">
         <v>37</v>
       </c>
       <c r="C13" s="35" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D13" s="35" t="str">
         <f>哥布林弹珠氪金!E20</f>
@@ -10250,7 +10250,7 @@
         <v>38</v>
       </c>
       <c r="C14" s="35" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>哥布林弹珠氪金!G20</f>
@@ -10283,7 +10283,7 @@
         <v>39</v>
       </c>
       <c r="C15" s="35" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D15" s="35" t="str">
         <f>哥布林弹珠氪金!I20</f>
@@ -10316,7 +10316,7 @@
         <v>40</v>
       </c>
       <c r="C16" s="35" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D16" s="35" t="str">
         <f>哥布林弹珠氪金!K20</f>
@@ -10349,7 +10349,7 @@
         <v>41</v>
       </c>
       <c r="C17" s="35" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D17" s="35" t="str">
         <f>哥布林弹珠氪金!M20</f>
@@ -10385,7 +10385,7 @@
         <v>42</v>
       </c>
       <c r="C18" s="47" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D18" s="48" t="str">
         <f>哥布林弹珠氪金!O20</f>
@@ -10439,7 +10439,7 @@
     </row>
     <row r="21" spans="1:18" ht="66" customHeight="1" thickBot="1">
       <c r="B21" s="130" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C21" s="131"/>
       <c r="D21" s="131"/>
